--- a/Software_Project_Template/05_Finance_and_Growth/unit_economics.xlsx
+++ b/Software_Project_Template/05_Finance_and_Growth/unit_economics.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nii Quaynor\projects\Maestro\Software_Project_Template\05_Finance_and_Growth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F63619A-A1F8-460F-916E-A47F517D6DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8022C9-72A8-4ABD-B649-07040D557F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Core_Unit_Economics" sheetId="1" r:id="rId1"/>
+    <sheet name="Acquisition_Model" sheetId="2" r:id="rId2"/>
+    <sheet name="Revenue_Model_Per_User" sheetId="3" r:id="rId3"/>
+    <sheet name="Cost_Per_User_Breakdown" sheetId="4" r:id="rId4"/>
+    <sheet name="Sensitivity_Analysis" sheetId="5" r:id="rId5"/>
+    <sheet name="Break_Even_Analysis" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,14 +30,354 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+  <si>
+    <t>Core_Unit_Economics</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Customer Acquisition Cost (CAC)</t>
+  </si>
+  <si>
+    <t>Total Marketing Spend / New Users</t>
+  </si>
+  <si>
+    <t>£</t>
+  </si>
+  <si>
+    <t>Input manually</t>
+  </si>
+  <si>
+    <t>Monthly Revenue per User (ARPU)</t>
+  </si>
+  <si>
+    <t>Total Revenue / Active Users</t>
+  </si>
+  <si>
+    <t>Core revenue driver</t>
+  </si>
+  <si>
+    <t>Cost per User (CPU)</t>
+  </si>
+  <si>
+    <t>Total Infra Cost / Active Users</t>
+  </si>
+  <si>
+    <t>From infrastructure_costs</t>
+  </si>
+  <si>
+    <t>Gross Margin</t>
+  </si>
+  <si>
+    <t>(ARPU - CPU) / ARPU</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Key profitability metric</t>
+  </si>
+  <si>
+    <t>Customer Lifetime (Months)</t>
+  </si>
+  <si>
+    <t>1 / Churn Rate</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>Assumes steady churn</t>
+  </si>
+  <si>
+    <t>Lifetime Value (LTV)</t>
+  </si>
+  <si>
+    <t>ARPU × Customer Lifetime</t>
+  </si>
+  <si>
+    <t>Revenue per user over time</t>
+  </si>
+  <si>
+    <t>LTV:CAC Ratio</t>
+  </si>
+  <si>
+    <t>LTV / CAC</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>Ideal: &gt;3</t>
+  </si>
+  <si>
+    <t>Payback Period</t>
+  </si>
+  <si>
+    <t>CAC / ARPU</t>
+  </si>
+  <si>
+    <t>Time to recover CAC</t>
+  </si>
+  <si>
+    <t>Acquisition_Model</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>Monthly Spend (£)</t>
+  </si>
+  <si>
+    <t>New Users Acquired</t>
+  </si>
+  <si>
+    <t>CAC (£)</t>
+  </si>
+  <si>
+    <t>Conversion Rate (%)</t>
+  </si>
+  <si>
+    <t>Organic</t>
+  </si>
+  <si>
+    <t>SEO / word of mouth</t>
+  </si>
+  <si>
+    <t>Paid Ads</t>
+  </si>
+  <si>
+    <t>Google / Meta</t>
+  </si>
+  <si>
+    <t>Partnerships</t>
+  </si>
+  <si>
+    <t>B2B integrations</t>
+  </si>
+  <si>
+    <t>Referrals</t>
+  </si>
+  <si>
+    <t>Incentivised growth</t>
+  </si>
+  <si>
+    <t>Revenue_Model_Per_User</t>
+  </si>
+  <si>
+    <t>Revenue Stream</t>
+  </si>
+  <si>
+    <t>Price (£)</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Monthly Equivalent (£)</t>
+  </si>
+  <si>
+    <t>% Users Using</t>
+  </si>
+  <si>
+    <t>Weighted Revenue (£)</t>
+  </si>
+  <si>
+    <t>Subscription (Basic)</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>Subscription (Premium)</t>
+  </si>
+  <si>
+    <t>Usage-Based Fees</t>
+  </si>
+  <si>
+    <t>Per Use</t>
+  </si>
+  <si>
+    <t>API Access</t>
+  </si>
+  <si>
+    <t>Add-ons</t>
+  </si>
+  <si>
+    <t>Total ARPU</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Cost_Per_User_Breakdown</t>
+  </si>
+  <si>
+    <t>Cost Category</t>
+  </si>
+  <si>
+    <t>Monthly Cost (£)</t>
+  </si>
+  <si>
+    <t>Active Users</t>
+  </si>
+  <si>
+    <t>Cost per User (£)</t>
+  </si>
+  <si>
+    <t>Compute</t>
+  </si>
+  <si>
+    <t>ECS / Lambda</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>RDS / Dynamo</t>
+  </si>
+  <si>
+    <t>AI (LLM)</t>
+  </si>
+  <si>
+    <t>Bedrock</t>
+  </si>
+  <si>
+    <t>API Costs</t>
+  </si>
+  <si>
+    <t>External APIs</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Logs + metrics</t>
+  </si>
+  <si>
+    <t>Total CPU</t>
+  </si>
+  <si>
+    <t>Sensitivity_Analysis</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Low Case</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>High Case</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Affects payback</t>
+  </si>
+  <si>
+    <t>ARPU (£)</t>
+  </si>
+  <si>
+    <t>Revenue scaling</t>
+  </si>
+  <si>
+    <t>Churn Rate (%)</t>
+  </si>
+  <si>
+    <t>Lifetime value</t>
+  </si>
+  <si>
+    <t>AI Cost per User (£)</t>
+  </si>
+  <si>
+    <t>Profitability risk</t>
+  </si>
+  <si>
+    <t>Break_Even_Analysis</t>
+  </si>
+  <si>
+    <t>Fixed Costs (£)</t>
+  </si>
+  <si>
+    <t>Infra baseline</t>
+  </si>
+  <si>
+    <t>From revenue model</t>
+  </si>
+  <si>
+    <t>Variable Cost per User (£)</t>
+  </si>
+  <si>
+    <t>From CPU</t>
+  </si>
+  <si>
+    <t>Contribution Margin</t>
+  </si>
+  <si>
+    <t>ARPU - CPU</t>
+  </si>
+  <si>
+    <t>Per user</t>
+  </si>
+  <si>
+    <t>Break-even Users</t>
+  </si>
+  <si>
+    <t>Fixed Costs / Contribution Margin</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Core scaling target</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,7 +392,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -55,12 +400,280 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -341,9 +954,1871 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="J2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29504693-8171-401D-A4D9-C199680BD993}">
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" spans="1:17" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="J2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2F9D0BF-3C26-4623-9310-6C79BDB549C6}">
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" spans="1:17" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="11">
+        <v>0</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="20">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="J2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D56055-17B9-4156-8B74-6D33DE9CDF4F}">
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" spans="1:17" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="11">
+        <v>0</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="11">
+        <v>0</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="J2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51BC1E6E-C336-40A7-8427-D1C298E7D106}">
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="11">
+        <v>5</v>
+      </c>
+      <c r="C4" s="11">
+        <v>15</v>
+      </c>
+      <c r="D4" s="11">
+        <v>40</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="11">
+        <v>2</v>
+      </c>
+      <c r="C5" s="11">
+        <v>10</v>
+      </c>
+      <c r="D5" s="11">
+        <v>25</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="11">
+        <v>5</v>
+      </c>
+      <c r="C6" s="11">
+        <v>10</v>
+      </c>
+      <c r="D6" s="11">
+        <v>25</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="11">
+        <v>2</v>
+      </c>
+      <c r="D7" s="11">
+        <v>8</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="J2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF94DBD0-A7C0-4A8D-B8EF-072C32C86C4B}">
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="J2:Q2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>